--- a/BA/Part 1_Stakeholder Analysis amp Management-20260912/TemplatesFinal/SH Management_Stakeholder Register_RACI Matrix_Power and Interest grid_Template.xlsx
+++ b/BA/Part 1_Stakeholder Analysis amp Management-20260912/TemplatesFinal/SH Management_Stakeholder Register_RACI Matrix_Power and Interest grid_Template.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -154,12 +154,6 @@
       <name val="Calibri"/>
       <sz val="8.5"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="008A8A8A"/>
-      <sz val="8.5"/>
-    </font>
   </fonts>
   <fills count="30">
     <fill>
@@ -289,12 +283,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
+        <fgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6E0B4"/>
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -721,7 +715,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -987,9 +981,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1750,12 +1741,12 @@
       </c>
       <c r="H9" s="59" t="inlineStr">
         <is>
-          <t>Official report</t>
+          <t>Monitoring of national regulation</t>
         </is>
       </c>
       <c r="I9" s="59" t="inlineStr">
         <is>
-          <t>Once per semester</t>
+          <t>Ad hoc, if regulation changes</t>
         </is>
       </c>
       <c r="J9" s="59" t="inlineStr">
@@ -1770,7 +1761,7 @@
       </c>
       <c r="L9" s="70" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M9" s="70" t="inlineStr">
@@ -1780,12 +1771,12 @@
       </c>
       <c r="N9" s="70" t="inlineStr">
         <is>
-          <t>Meet their needs</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="O9" s="59" t="inlineStr">
         <is>
-          <t>Not involved in day-to-day work, but defines the regulatory requirements for educational IT systems and sector funding. Communication is formal reporting at control points only.</t>
+          <t>Formal sponsor of the sector, but for a pilot inside a single department the ministry has neither influence over delivery nor day-to-day interest in it. Monitored only in case the national regulation of educational IT systems changes; no recurring communication and no project activity is assigned to it.</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2081,7 @@
       </c>
       <c r="D14" s="71" t="inlineStr">
         <is>
-          <t>Project team “VNS”, group SHI-2025</t>
+          <t>Project team “20/80”, group SHI-2025</t>
         </is>
       </c>
       <c r="E14" s="71" t="inlineStr">
@@ -2162,7 +2153,7 @@
       </c>
       <c r="D15" s="71" t="inlineStr">
         <is>
-          <t>Project team “VNS”, group SHI-2025</t>
+          <t>Project team “20/80”, group SHI-2025</t>
         </is>
       </c>
       <c r="E15" s="71" t="inlineStr">
@@ -2234,7 +2225,7 @@
       </c>
       <c r="D16" s="71" t="inlineStr">
         <is>
-          <t>Project team “VNS”, group SHI-2025</t>
+          <t>Project team “20/80”, group SHI-2025</t>
         </is>
       </c>
       <c r="E16" s="71" t="inlineStr">
@@ -2306,7 +2297,7 @@
       </c>
       <c r="D17" s="71" t="inlineStr">
         <is>
-          <t>Project team “VNS”, group SHI-2025</t>
+          <t>Project team “20/80”, group SHI-2025</t>
         </is>
       </c>
       <c r="E17" s="71" t="inlineStr">
@@ -2378,7 +2369,7 @@
       </c>
       <c r="D18" s="71" t="inlineStr">
         <is>
-          <t>Project team “VNS”, group SHI-2025</t>
+          <t>Project team “20/80”, group SHI-2025</t>
         </is>
       </c>
       <c r="E18" s="71" t="inlineStr">
@@ -2450,7 +2441,7 @@
       </c>
       <c r="D19" s="71" t="inlineStr">
         <is>
-          <t>Project team “VNS”, group SHI-2025</t>
+          <t>Project team “20/80”, group SHI-2025</t>
         </is>
       </c>
       <c r="E19" s="71" t="inlineStr">
@@ -2613,7 +2604,6 @@
     <col width="6.6" customWidth="1" min="11" max="11"/>
     <col width="6.6" customWidth="1" min="12" max="12"/>
     <col width="6.6" customWidth="1" min="13" max="13"/>
-    <col width="6.6" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" thickBot="1">
@@ -2688,64 +2678,60 @@
       </c>
       <c r="C6" s="89" t="inlineStr">
         <is>
-          <t>Lviv Polytechnic National University (Sponsor)</t>
+          <t>Lviv Polytechnic National University (Project Sponsor)</t>
         </is>
       </c>
       <c r="D6" s="89" t="inlineStr">
         <is>
-          <t>Ministry of Education and Science (Sponsor)</t>
+          <t>Nataliia Shakhovska (Executive Sponsor, Rector)</t>
         </is>
       </c>
       <c r="E6" s="89" t="inlineStr">
         <is>
-          <t>Nataliia Shakhovska (Rector)</t>
+          <t>Product Owner (K. Holovskyi)</t>
         </is>
       </c>
       <c r="F6" s="89" t="inlineStr">
         <is>
+          <t>Project Manager (N. Zankovych)</t>
+        </is>
+      </c>
+      <c r="G6" s="89" t="inlineStr">
+        <is>
+          <t>Business Analyst (A. Lysun)</t>
+        </is>
+      </c>
+      <c r="H6" s="89" t="inlineStr">
+        <is>
+          <t>Tech Lead (D. Lunhul)</t>
+        </is>
+      </c>
+      <c r="I6" s="89" t="inlineStr">
+        <is>
+          <t>DevOps (Y. Shevchuk)</t>
+        </is>
+      </c>
+      <c r="J6" s="89" t="inlineStr">
+        <is>
+          <t>QA Specialist (V. Kamelchuk)</t>
+        </is>
+      </c>
+      <c r="K6" s="89" t="inlineStr">
+        <is>
           <t>Nataliia Boiko (Customer / End user)</t>
         </is>
       </c>
-      <c r="G6" s="89" t="inlineStr">
+      <c r="L6" s="89" t="inlineStr">
         <is>
           <t>Technical Department of Lviv Polytechnic</t>
         </is>
       </c>
-      <c r="H6" s="89" t="inlineStr">
+      <c r="M6" s="89" t="inlineStr">
         <is>
           <t>End users — students</t>
         </is>
       </c>
-      <c r="I6" s="89" t="inlineStr">
-        <is>
-          <t>Product Owner (K. Holovskyi)</t>
-        </is>
-      </c>
-      <c r="J6" s="89" t="inlineStr">
-        <is>
-          <t>Project Manager (N. Zankovych)</t>
-        </is>
-      </c>
-      <c r="K6" s="89" t="inlineStr">
-        <is>
-          <t>Business Analyst (A. Lysun)</t>
-        </is>
-      </c>
-      <c r="L6" s="89" t="inlineStr">
-        <is>
-          <t>Tech Lead (D. Lunhul)</t>
-        </is>
-      </c>
-      <c r="M6" s="89" t="inlineStr">
-        <is>
-          <t>DevOps (Y. Shevchuk)</t>
-        </is>
-      </c>
-      <c r="N6" s="89" t="inlineStr">
-        <is>
-          <t>QA Specialist (V. Kamelchuk)</t>
-        </is>
-      </c>
+      <c r="N6" s="29" t="n"/>
       <c r="O6" s="29" t="n"/>
       <c r="P6" s="54" t="n"/>
     </row>
@@ -2792,56 +2778,52 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E8" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="E8" s="96" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="F8" s="96" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G8" s="96" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H8" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I8" s="97" t="inlineStr">
-        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="J8" s="97" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="H8" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I8" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J8" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="K8" s="97" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L8" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M8" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="N8" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L8" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M8" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N8" s="36" t="n"/>
       <c r="O8" s="36" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -2851,7 +2833,7 @@
           <t>Identify and analyse stakeholders (register, power/interest matrix)</t>
         </is>
       </c>
-      <c r="C9" s="96" t="inlineStr">
+      <c r="C9" s="97" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2861,19 +2843,19 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E9" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F9" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G9" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="E9" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F9" s="94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G9" s="96" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="H9" s="95" t="inlineStr">
@@ -2881,19 +2863,19 @@
           <t>I</t>
         </is>
       </c>
-      <c r="I9" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J9" s="94" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="I9" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J9" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="K9" s="97" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="L9" s="95" t="inlineStr">
@@ -2906,11 +2888,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="N9" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="N9" s="32" t="n"/>
       <c r="O9" s="32" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
@@ -2930,56 +2908,52 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E10" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F10" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G10" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H10" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="E10" s="96" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F10" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G10" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="96" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="I10" s="97" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J10" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K10" s="96" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J10" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K10" s="97" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="L10" s="97" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M10" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N10" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M10" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="N10" s="32" t="n"/>
       <c r="O10" s="32" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
@@ -2989,54 +2963,54 @@
           <t>Develop the business case and the success metrics</t>
         </is>
       </c>
-      <c r="C11" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D11" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E11" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="C11" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D11" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E11" s="94" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="F11" s="96" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G11" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H11" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I11" s="94" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J11" s="97" t="inlineStr">
-        <is>
           <t>R</t>
         </is>
       </c>
+      <c r="G11" s="96" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H11" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I11" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J11" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="K11" s="97" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L11" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L11" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="M11" s="95" t="inlineStr">
@@ -3044,11 +3018,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="N11" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="N11" s="32" t="n"/>
       <c r="O11" s="32" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
@@ -3058,54 +3028,54 @@
           <t>Approve the project charter and the MVP scope</t>
         </is>
       </c>
-      <c r="C12" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D12" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E12" s="94" t="inlineStr">
+      <c r="C12" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D12" s="94" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
+      <c r="E12" s="96" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="F12" s="96" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G12" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H12" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I12" s="97" t="inlineStr">
-        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="J12" s="97" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K12" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L12" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="G12" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I12" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J12" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K12" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L12" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="M12" s="95" t="inlineStr">
@@ -3113,11 +3083,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="N12" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="N12" s="32" t="n"/>
       <c r="O12" s="32" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
@@ -3137,52 +3103,52 @@
         </is>
       </c>
       <c r="D13" s="59" t="n"/>
-      <c r="E13" s="59" t="n"/>
-      <c r="F13" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G13" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H13" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I13" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J13" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K13" s="94" t="inlineStr">
+      <c r="E13" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F13" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G13" s="94" t="inlineStr">
         <is>
           <t>R/A</t>
         </is>
       </c>
-      <c r="L13" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M13" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="N13" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="H13" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I13" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J13" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K13" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L13" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M13" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N13" s="32" t="n"/>
       <c r="O13" s="32" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
@@ -3198,40 +3164,44 @@
         </is>
       </c>
       <c r="D14" s="59" t="n"/>
-      <c r="E14" s="59" t="n"/>
-      <c r="F14" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G14" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H14" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I14" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J14" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K14" s="94" t="inlineStr">
+      <c r="E14" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F14" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G14" s="94" t="inlineStr">
         <is>
           <t>R/A</t>
         </is>
       </c>
-      <c r="L14" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="H14" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I14" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J14" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K14" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L14" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="M14" s="95" t="inlineStr">
@@ -3239,11 +3209,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="N14" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="N14" s="32" t="n"/>
       <c r="O14" s="32" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
@@ -3259,48 +3225,48 @@
         </is>
       </c>
       <c r="D15" s="59" t="n"/>
-      <c r="E15" s="59" t="n"/>
-      <c r="F15" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G15" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H15" s="59" t="n"/>
+      <c r="E15" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F15" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G15" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H15" s="94" t="inlineStr">
+        <is>
+          <t>R/A</t>
+        </is>
+      </c>
       <c r="I15" s="96" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J15" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K15" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L15" s="94" t="inlineStr">
-        <is>
-          <t>R/A</t>
-        </is>
-      </c>
-      <c r="M15" s="97" t="inlineStr">
-        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="N15" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="J15" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K15" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="L15" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M15" s="59" t="n"/>
+      <c r="N15" s="32" t="n"/>
       <c r="O15" s="32" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
@@ -3315,61 +3281,57 @@
           <t>A</t>
         </is>
       </c>
-      <c r="D16" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E16" s="96" t="inlineStr">
+      <c r="D16" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E16" s="97" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="F16" s="96" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G16" s="96" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H16" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I16" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J16" s="97" t="inlineStr">
-        <is>
           <t>R</t>
         </is>
       </c>
+      <c r="H16" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I16" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J16" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="K16" s="97" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L16" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M16" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N16" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L16" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M16" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="N16" s="32" t="n"/>
       <c r="O16" s="32" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
@@ -3379,7 +3341,7 @@
           <t>Produce the communications plan and the project schedule</t>
         </is>
       </c>
-      <c r="C17" s="96" t="inlineStr">
+      <c r="C17" s="97" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -3389,56 +3351,52 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E17" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F17" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G17" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H17" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I17" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J17" s="94" t="inlineStr">
+      <c r="E17" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F17" s="94" t="inlineStr">
         <is>
           <t>R/A</t>
         </is>
       </c>
+      <c r="G17" s="96" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H17" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I17" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J17" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="K17" s="97" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L17" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M17" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N17" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L17" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="M17" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="N17" s="32" t="n"/>
       <c r="O17" s="32" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
@@ -3448,58 +3406,58 @@
           <t>Select the technology stack and the LLM API provider</t>
         </is>
       </c>
-      <c r="C18" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D18" s="59" t="n"/>
-      <c r="E18" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F18" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G18" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H18" s="59" t="n"/>
+      <c r="C18" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D18" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E18" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F18" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G18" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H18" s="94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="I18" s="96" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J18" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K18" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L18" s="94" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="M18" s="97" t="inlineStr">
-        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="N18" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="J18" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K18" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="L18" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M18" s="59" t="n"/>
+      <c r="N18" s="32" t="n"/>
       <c r="O18" s="32" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
@@ -3513,58 +3471,58 @@
           <t>Obtain the student registry; implement registration and authentication</t>
         </is>
       </c>
-      <c r="C19" s="96" t="inlineStr">
+      <c r="C19" s="97" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="D19" s="59" t="n"/>
-      <c r="E19" s="59" t="n"/>
-      <c r="F19" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="E19" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F19" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="G19" s="97" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H19" s="94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I19" s="96" t="inlineStr">
+        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H19" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I19" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J19" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K19" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L19" s="94" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="M19" s="97" t="inlineStr">
+      <c r="J19" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K19" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="L19" s="96" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="N19" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="M19" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="N19" s="32" t="n"/>
       <c r="O19" s="32" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
@@ -3580,52 +3538,52 @@
         </is>
       </c>
       <c r="D20" s="59" t="n"/>
-      <c r="E20" s="59" t="n"/>
-      <c r="F20" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G20" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H20" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I20" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J20" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K20" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L20" s="94" t="inlineStr">
+      <c r="E20" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F20" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G20" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H20" s="94" t="inlineStr">
         <is>
           <t>R/A</t>
         </is>
       </c>
+      <c r="I20" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J20" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K20" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L20" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="M20" s="95" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="N20" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="N20" s="32" t="n"/>
       <c r="O20" s="32" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -3641,52 +3599,52 @@
         </is>
       </c>
       <c r="D21" s="59" t="n"/>
-      <c r="E21" s="59" t="n"/>
-      <c r="F21" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G21" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H21" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="E21" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F21" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G21" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H21" s="94" t="inlineStr">
+        <is>
+          <t>R/A</t>
         </is>
       </c>
       <c r="I21" s="96" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J21" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K21" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L21" s="94" t="inlineStr">
-        <is>
-          <t>R/A</t>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J21" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K21" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L21" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="M21" s="97" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="N21" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N21" s="32" t="n"/>
       <c r="O21" s="32" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
@@ -3702,52 +3660,52 @@
         </is>
       </c>
       <c r="D22" s="59" t="n"/>
-      <c r="E22" s="59" t="n"/>
-      <c r="F22" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G22" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="E22" s="94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F22" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G22" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="H22" s="96" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I22" s="94" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J22" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K22" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L22" s="97" t="inlineStr">
-        <is>
           <t>R</t>
         </is>
       </c>
+      <c r="I22" s="96" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J22" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K22" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L22" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="M22" s="97" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="N22" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N22" s="32" t="n"/>
       <c r="O22" s="32" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
@@ -3763,44 +3721,44 @@
         </is>
       </c>
       <c r="D23" s="59" t="n"/>
-      <c r="E23" s="59" t="n"/>
-      <c r="F23" s="59" t="n"/>
-      <c r="G23" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H23" s="59" t="n"/>
-      <c r="I23" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J23" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K23" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="L23" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M23" s="94" t="inlineStr">
+      <c r="E23" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F23" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G23" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H23" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I23" s="94" t="inlineStr">
         <is>
           <t>R/A</t>
         </is>
       </c>
-      <c r="N23" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="J23" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K23" s="59" t="n"/>
+      <c r="L23" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M23" s="59" t="n"/>
+      <c r="N23" s="32" t="n"/>
       <c r="O23" s="32" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
@@ -3816,52 +3774,52 @@
         </is>
       </c>
       <c r="D24" s="59" t="n"/>
-      <c r="E24" s="59" t="n"/>
-      <c r="F24" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G24" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H24" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I24" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J24" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K24" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L24" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M24" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N24" s="94" t="inlineStr">
+      <c r="E24" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F24" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G24" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H24" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I24" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J24" s="94" t="inlineStr">
         <is>
           <t>R/A</t>
         </is>
       </c>
+      <c r="K24" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L24" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="M24" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N24" s="32" t="n"/>
       <c r="O24" s="32" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
@@ -3875,7 +3833,7 @@
           <t>Manage scope changes and backlog priorities</t>
         </is>
       </c>
-      <c r="C25" s="96" t="inlineStr">
+      <c r="C25" s="97" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -3885,44 +3843,44 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E25" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="E25" s="94" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="F25" s="96" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G25" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H25" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I25" s="94" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J25" s="97" t="inlineStr">
-        <is>
           <t>R</t>
         </is>
       </c>
+      <c r="G25" s="96" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H25" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I25" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J25" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="K25" s="97" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L25" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L25" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="M25" s="95" t="inlineStr">
@@ -3930,11 +3888,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="N25" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="N25" s="32" t="n"/>
       <c r="O25" s="32" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
@@ -3950,52 +3904,52 @@
         </is>
       </c>
       <c r="D26" s="59" t="n"/>
-      <c r="E26" s="59" t="n"/>
-      <c r="F26" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G26" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H26" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I26" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J26" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K26" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L26" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M26" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="N26" s="94" t="inlineStr">
+      <c r="E26" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F26" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G26" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H26" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I26" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J26" s="94" t="inlineStr">
         <is>
           <t>R/A</t>
         </is>
       </c>
+      <c r="K26" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L26" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="M26" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N26" s="32" t="n"/>
       <c r="O26" s="32" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
@@ -4005,7 +3959,7 @@
           <t>Monitor LLM API costs, quotas and request limits</t>
         </is>
       </c>
-      <c r="C27" s="96" t="inlineStr">
+      <c r="C27" s="97" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -4015,44 +3969,40 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E27" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F27" s="59" t="n"/>
+      <c r="E27" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F27" s="94" t="inlineStr">
+        <is>
+          <t>R/A</t>
+        </is>
+      </c>
       <c r="G27" s="95" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="H27" s="59" t="n"/>
+      <c r="H27" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="I27" s="96" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J27" s="94" t="inlineStr">
-        <is>
-          <t>R/A</t>
-        </is>
-      </c>
-      <c r="K27" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="L27" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M27" s="97" t="inlineStr">
-        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="N27" s="59" t="n"/>
+      <c r="J27" s="59" t="n"/>
+      <c r="K27" s="59" t="n"/>
+      <c r="L27" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="M27" s="59" t="n"/>
+      <c r="N27" s="32" t="n"/>
       <c r="O27" s="32" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
@@ -4072,44 +4022,44 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E28" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F28" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G28" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H28" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I28" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J28" s="94" t="inlineStr">
+      <c r="E28" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F28" s="94" t="inlineStr">
         <is>
           <t>R/A</t>
         </is>
       </c>
-      <c r="K28" s="97" t="inlineStr">
+      <c r="G28" s="96" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="L28" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="H28" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I28" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J28" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K28" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="L28" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="M28" s="95" t="inlineStr">
@@ -4117,11 +4067,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="N28" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="N28" s="32" t="n"/>
       <c r="O28" s="32" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
@@ -4135,7 +4081,7 @@
           <t>Run the pilot with students and collect feedback</t>
         </is>
       </c>
-      <c r="C29" s="96" t="inlineStr">
+      <c r="C29" s="97" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -4145,56 +4091,52 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E29" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F29" s="97" t="inlineStr">
+      <c r="E29" s="94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F29" s="96" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="G29" s="96" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H29" s="97" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I29" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J29" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K29" s="96" t="inlineStr">
+        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="I29" s="94" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J29" s="97" t="inlineStr">
+      <c r="L29" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M29" s="96" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="K29" s="97" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L29" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M29" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N29" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="N29" s="32" t="n"/>
       <c r="O29" s="32" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
@@ -4204,66 +4146,62 @@
           <t>Hand over the system and documentation to the Technical Department and the customer</t>
         </is>
       </c>
-      <c r="C30" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D30" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="C30" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D30" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="E30" s="96" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F30" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G30" s="97" t="inlineStr">
-        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H30" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I30" s="97" t="inlineStr">
+      <c r="F30" s="94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G30" s="96" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="J30" s="94" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="H30" s="96" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I30" s="96" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J30" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="K30" s="97" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L30" s="96" t="inlineStr">
+        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="L30" s="97" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M30" s="97" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="N30" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="M30" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="N30" s="32" t="n"/>
       <c r="O30" s="32" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
@@ -4273,7 +4211,7 @@
           <t>Capture lessons learned and close the project</t>
         </is>
       </c>
-      <c r="C31" s="96" t="inlineStr">
+      <c r="C31" s="97" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -4283,56 +4221,52 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E31" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F31" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="E31" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F31" s="94" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="G31" s="96" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H31" s="95" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I31" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J31" s="94" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H31" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I31" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J31" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="K31" s="97" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L31" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M31" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N31" s="96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L31" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M31" s="95" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="N31" s="32" t="n"/>
       <c r="O31" s="32" t="n"/>
     </row>
     <row r="32">
@@ -5024,19 +4958,16 @@
     <row r="4" ht="15" customHeight="1">
       <c r="B4" s="103" t="inlineStr">
         <is>
-          <t>Ministry of
-Education and
-Science (Sponsor)</t>
-        </is>
-      </c>
-      <c r="F4" s="101" t="n"/>
-      <c r="G4" s="103" t="inlineStr">
-        <is>
           <t>Nataliia
 Shakhovska
 Rector</t>
         </is>
       </c>
+      <c r="F4" s="101" t="n"/>
+      <c r="G4" s="101" t="n"/>
+      <c r="H4" s="101" t="n"/>
+      <c r="I4" s="101" t="n"/>
+      <c r="J4" s="101" t="n"/>
       <c r="K4" s="101" t="n"/>
       <c r="L4" s="101" t="n"/>
       <c r="M4" s="101" t="n"/>
@@ -5068,6 +4999,10 @@
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="F5" s="101" t="n"/>
+      <c r="G5" s="101" t="n"/>
+      <c r="H5" s="101" t="n"/>
+      <c r="I5" s="101" t="n"/>
+      <c r="J5" s="101" t="n"/>
       <c r="K5" s="101" t="n"/>
       <c r="L5" s="101" t="n"/>
       <c r="M5" s="101" t="n"/>
@@ -5078,6 +5013,10 @@
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="F6" s="101" t="n"/>
+      <c r="G6" s="101" t="n"/>
+      <c r="H6" s="101" t="n"/>
+      <c r="I6" s="101" t="n"/>
+      <c r="J6" s="101" t="n"/>
       <c r="K6" s="101" t="n"/>
       <c r="L6" s="101" t="n"/>
       <c r="M6" s="101" t="n"/>
@@ -5641,11 +5580,18 @@
       <c r="AC25" s="101" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="107" t="inlineStr">
-        <is>
-          <t>— no stakeholders in this quadrant: the approved list contains nobody with both low influence and low interest —</t>
-        </is>
-      </c>
+      <c r="B26" s="103" t="inlineStr">
+        <is>
+          <t>Ministry of
+Education and
+Science (Sponsor)</t>
+        </is>
+      </c>
+      <c r="F26" s="101" t="n"/>
+      <c r="G26" s="101" t="n"/>
+      <c r="H26" s="101" t="n"/>
+      <c r="I26" s="101" t="n"/>
+      <c r="J26" s="101" t="n"/>
       <c r="K26" s="101" t="n"/>
       <c r="L26" s="101" t="n"/>
       <c r="M26" s="101" t="n"/>
@@ -5673,6 +5619,11 @@
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
+      <c r="F27" s="101" t="n"/>
+      <c r="G27" s="101" t="n"/>
+      <c r="H27" s="101" t="n"/>
+      <c r="I27" s="101" t="n"/>
+      <c r="J27" s="101" t="n"/>
       <c r="K27" s="101" t="n"/>
       <c r="L27" s="101" t="n"/>
       <c r="M27" s="101" t="n"/>
@@ -5682,6 +5633,11 @@
       <c r="Y27" s="101" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
+      <c r="F28" s="101" t="n"/>
+      <c r="G28" s="101" t="n"/>
+      <c r="H28" s="101" t="n"/>
+      <c r="I28" s="101" t="n"/>
+      <c r="J28" s="101" t="n"/>
       <c r="K28" s="101" t="n"/>
       <c r="L28" s="101" t="n"/>
       <c r="M28" s="101" t="n"/>
@@ -6141,33 +6097,32 @@
       <c r="AC43" s="101" t="n"/>
     </row>
     <row r="44" ht="31.5" customFormat="1" customHeight="1" s="2">
-      <c r="A44" s="108" t="inlineStr">
+      <c r="A44" s="107" t="inlineStr">
         <is>
           <t>low                                                                                               INTEREST                                                                                             high</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="18">
+    <mergeCell ref="V1:X2"/>
+    <mergeCell ref="F23:H24"/>
     <mergeCell ref="A44:AC44"/>
-    <mergeCell ref="Z8:AC10"/>
     <mergeCell ref="F1:H2"/>
     <mergeCell ref="U8:X10"/>
-    <mergeCell ref="G4:J6"/>
     <mergeCell ref="Z4:AC6"/>
+    <mergeCell ref="Z8:AC10"/>
+    <mergeCell ref="B26:E28"/>
     <mergeCell ref="P12:S14"/>
+    <mergeCell ref="P4:S6"/>
+    <mergeCell ref="P26:S28"/>
+    <mergeCell ref="B4:E6"/>
     <mergeCell ref="U26:X28"/>
-    <mergeCell ref="B4:E6"/>
+    <mergeCell ref="Z26:AC28"/>
     <mergeCell ref="U4:X6"/>
+    <mergeCell ref="P8:S10"/>
     <mergeCell ref="A1:A43"/>
     <mergeCell ref="V23:X24"/>
-    <mergeCell ref="V1:X2"/>
-    <mergeCell ref="P26:S28"/>
-    <mergeCell ref="P4:S6"/>
-    <mergeCell ref="Z26:AC28"/>
-    <mergeCell ref="B26:J28"/>
-    <mergeCell ref="F23:H24"/>
-    <mergeCell ref="P8:S10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/BA/Part 1_Stakeholder Analysis amp Management-20260912/TemplatesFinal/SH Management_Stakeholder Register_RACI Matrix_Power and Interest grid_Template.xlsx
+++ b/BA/Part 1_Stakeholder Analysis amp Management-20260912/TemplatesFinal/SH Management_Stakeholder Register_RACI Matrix_Power and Interest grid_Template.xlsx
@@ -1367,20 +1367,20 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="19.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="19.85546875" customWidth="1" style="14" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="34" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="26" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="62" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="40" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="30" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="70" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1636,7 +1636,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="62" customHeight="1">
+    <row r="8" ht="74" customHeight="1">
       <c r="B8" s="59" t="inlineStr">
         <is>
           <t>Lviv Polytechnic National University</t>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="62" customHeight="1">
+    <row r="9" ht="74" customHeight="1">
       <c r="B9" s="59" t="inlineStr">
         <is>
           <t>Ministry of Education and Science of Ukraine</t>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="62" customHeight="1">
+    <row r="10" ht="74" customHeight="1">
       <c r="B10" s="59" t="inlineStr">
         <is>
           <t>Nataliia Shakhovska</t>
@@ -1852,7 +1852,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="62" customHeight="1">
+    <row r="11" ht="74" customHeight="1">
       <c r="B11" s="59" t="inlineStr">
         <is>
           <t>Nataliia Boiko</t>
@@ -1924,7 +1924,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="62" customHeight="1">
+    <row r="12" ht="74" customHeight="1">
       <c r="B12" s="59" t="inlineStr">
         <is>
           <t>Technical Department of Lviv Polytechnic</t>
@@ -1996,7 +1996,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="62" customHeight="1">
+    <row r="13" ht="74" customHeight="1">
       <c r="B13" s="59" t="inlineStr">
         <is>
           <t>End users — Lviv Polytechnic students</t>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="62" customHeight="1">
+    <row r="14" ht="74" customHeight="1">
       <c r="B14" s="71" t="inlineStr">
         <is>
           <t>Kostiantyn Holovskyi</t>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D14" s="71" t="inlineStr">
         <is>
-          <t>Project team “20/80”, group SHI-2025</t>
+          <t>Project team “20/80”</t>
         </is>
       </c>
       <c r="E14" s="71" t="inlineStr">
@@ -2140,7 +2140,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="62" customHeight="1">
+    <row r="15" ht="74" customHeight="1">
       <c r="B15" s="71" t="inlineStr">
         <is>
           <t>Nazar Zankovych</t>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="D15" s="71" t="inlineStr">
         <is>
-          <t>Project team “20/80”, group SHI-2025</t>
+          <t>Project team “20/80”</t>
         </is>
       </c>
       <c r="E15" s="71" t="inlineStr">
@@ -2212,7 +2212,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="62" customHeight="1">
+    <row r="16" ht="74" customHeight="1">
       <c r="B16" s="71" t="inlineStr">
         <is>
           <t>Andrii Lysun</t>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="D16" s="71" t="inlineStr">
         <is>
-          <t>Project team “20/80”, group SHI-2025</t>
+          <t>Project team “20/80”</t>
         </is>
       </c>
       <c r="E16" s="71" t="inlineStr">
@@ -2284,7 +2284,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="62" customHeight="1">
+    <row r="17" ht="74" customHeight="1">
       <c r="B17" s="71" t="inlineStr">
         <is>
           <t>Denys Lunhul</t>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D17" s="71" t="inlineStr">
         <is>
-          <t>Project team “20/80”, group SHI-2025</t>
+          <t>Project team “20/80”</t>
         </is>
       </c>
       <c r="E17" s="71" t="inlineStr">
@@ -2356,7 +2356,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="62" customHeight="1">
+    <row r="18" ht="74" customHeight="1">
       <c r="B18" s="71" t="inlineStr">
         <is>
           <t>Yaroslav Shevchuk</t>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="D18" s="71" t="inlineStr">
         <is>
-          <t>Project team “20/80”, group SHI-2025</t>
+          <t>Project team “20/80”</t>
         </is>
       </c>
       <c r="E18" s="71" t="inlineStr">
@@ -2428,7 +2428,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="62" customHeight="1">
+    <row r="19" ht="74" customHeight="1">
       <c r="B19" s="71" t="inlineStr">
         <is>
           <t>Volodymyr Kamelchuk</t>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="D19" s="71" t="inlineStr">
         <is>
-          <t>Project team “20/80”, group SHI-2025</t>
+          <t>Project team “20/80”</t>
         </is>
       </c>
       <c r="E19" s="71" t="inlineStr">
@@ -2592,7 +2592,7 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="18.42578125" defaultRowHeight="23.25"/>
   <cols>
     <col width="26" customWidth="1" style="4" min="1" max="1"/>
-    <col width="62" bestFit="1" customWidth="1" style="6" min="2" max="2"/>
+    <col width="72" bestFit="1" customWidth="1" style="6" min="2" max="2"/>
     <col width="6.6" customWidth="1" style="5" min="3" max="16384"/>
     <col width="6.6" customWidth="1" min="4" max="4"/>
     <col width="6.6" customWidth="1" min="5" max="5"/>
